--- a/GPay_QA_Test_Cases.xlsx
+++ b/GPay_QA_Test_Cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shafiq/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC6C784-C9D0-1247-947B-AC64271F1DA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE6BFE62-A573-344F-B542-24A325CA7F3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Cases" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="339">
   <si>
     <t>Google Pay (GPay) – Manual QA Test Cases</t>
   </si>
@@ -114,19 +114,10 @@
     <t>App launches within 3 seconds; home screen visible</t>
   </si>
   <si>
-    <t>(fill during test)</t>
-  </si>
-  <si>
-    <t>(Pass / Fail / Blocked / Skip)</t>
-  </si>
-  <si>
     <t>High</t>
   </si>
   <si>
     <t>Critical</t>
-  </si>
-  <si>
-    <t>e.g. Samsung Galaxy S23</t>
   </si>
   <si>
     <t>TC002</t>
@@ -779,9 +770,6 @@
     <t>Steps to Reproduce</t>
   </si>
   <si>
-    <t>Screenshot/Video</t>
-  </si>
-  <si>
     <t>OS Version</t>
   </si>
   <si>
@@ -792,12 +780,6 @@
   </si>
   <si>
     <t>BUG-001</t>
-  </si>
-  <si>
-    <t>(Date)</t>
-  </si>
-  <si>
-    <t>(Module)</t>
   </si>
   <si>
     <t>(Bug title here)</t>
@@ -823,18 +805,9 @@
     <t>(New/Open/Fixed/Closed)</t>
   </si>
   <si>
-    <t>(link or filename)</t>
-  </si>
-  <si>
-    <t>(e.g., Android 14)</t>
-  </si>
-  <si>
     <t>(e.g., 245.0)</t>
   </si>
   <si>
-    <t>(e.g., Redmi Note 12)</t>
-  </si>
-  <si>
     <t>Mohammed Shafiq</t>
   </si>
   <si>
@@ -887,13 +860,308 @@
   </si>
   <si>
     <t>Pass Rate %</t>
+  </si>
+  <si>
+    <t>App launched successfully in ~2 seconds. GPay home screen displayed with all icons visible. No crash or delay observed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pass </t>
+  </si>
+  <si>
+    <t xml:space="preserve">App displayed "No internet connection" banner at top. App did not crash. Retry option was visible.
+</t>
+  </si>
+  <si>
+    <t>Entered registered mobile number, received OTP within 10 seconds, entered OTP, logged in successfully. Home screen displayed correctly.</t>
+  </si>
+  <si>
+    <t>App displayed "This number isn't registered on GPay" message. Prompted to set up a new account. Did not allow login.</t>
+  </si>
+  <si>
+    <t>Error message "Incorrect OTP" appeared in red. Login was blocked. "Resend OTP" option was displayed below.</t>
+  </si>
+  <si>
+    <t>After waiting 10 minutes, entered old OTP. App showed "OTP has expired. Please request a new one." Resend button was visible.</t>
+  </si>
+  <si>
+    <t>Entered valid UPI ID, amount ₹1, tapped Pay. Entered UPI PIN. Transaction successful screen appeared with green tick. Notification received on phone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entered recipient mobile number. GPay detected the contact. Entered ₹1, tapped Pay, entered PIN. "Payment Successful" screen shown. SMS notification received.
+</t>
+  </si>
+  <si>
+    <t>Entered amount greater than bank balance. After entering UPI PIN, app showed "Transaction failed – Insufficient funds" message in red. No money was deducted.</t>
+  </si>
+  <si>
+    <t>Entered ₹0 as amount. The Pay button was greyed out and disabled. Could not proceed. Message showed "Enter an amount."</t>
+  </si>
+  <si>
+    <t>App displayed "Transaction limit exceeded. UPI daily limit is ₹1,00,000" message. Payment was blocked. No amount was deducted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> After entering fake UPI ID and tapping Verify, app showed "Invalid UPI ID. Please check and try again." Payment screen did not proceed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tapped Request, selected contact, entered amount and note, tapped Request. Contact received a notification. Request showed as "Pending" in transaction history.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Selected electricity provider, entered account number, bill amount fetched automatically. Tapped Pay, entered UPI PIN. "Bill paid successfully" confirmation screen shown with receipt</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Entered invalid electricity account number, tapped Fetch Bill. App showed "Account not found. Please check your account number." Could not proceed to payment</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Entered own mobile number, operator detected automatically, selected plan, tapped Pay, entered UPI PIN. Recharge successful screen shown. Confirmation SMS received within 1 minute.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Entered different mobile number, selected operator and plan manually, tapped Pay. Recharge successful for the entered number. Confirmation shown on screen</t>
+  </si>
+  <si>
+    <t>Tapped Scan QR, camera opened instantly. Pointed at valid GPay QR code, merchant name and UPI ID appeared automatically. Entered amount, tapped Pay, entered PIN. Payment successful screen shown with green tick</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Pointed camera at a damaged QR code. App showed "Could not read QR code. Please try again or enter UPI ID manually." No payment was initiated.</t>
+  </si>
+  <si>
+    <t>Tapped profile icon, selected transaction history. All past transactions listed with date, amount, recipient name, and status (Success/Failed). Tapped one transaction — full detail view opened correctly</t>
+  </si>
+  <si>
+    <t>Opened transaction history, tapped filter icon, selected a custom date range, tapped Apply. Only transactions within selected dates were displayed. Transactions outside range were hidden</t>
+  </si>
+  <si>
+    <t>Went to Settings &gt; Bank Accounts &gt; Add Bank Account. Selected bank, app sent OTP to registered mobile number, verified successfully. New bank account appeared in the account list</t>
+  </si>
+  <si>
+    <t>Selected bank account from list, tapped Remove, confirmation dialog appeared. Tapped Confirm. Account was removed and no longer visible in the bank accounts list.</t>
+  </si>
+  <si>
+    <t>Went to bank account settings, tapped Change UPI PIN, entered old PIN, entered new PIN twice. "UPI PIN changed successfully" confirmation shown.</t>
+  </si>
+  <si>
+    <t>Entered wrong UPI PIN 3 consecutive times during a payment. App showed "Your UPI PIN has been blocked due to multiple incorrect attempts. Please reset your PIN." Payment was cancelled</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Completed a ₹1 payment and minimized the app. Push notification appeared on lock screen within 5 seconds showing recipient name and amount. Tapping notification opened GPay transaction detail.</t>
+  </si>
+  <si>
+    <t>Tapped Offers section from home screen. List of available cashback offers displayed with offer title, eligible transaction type, expiry date, and terms. All offers had valid expiry dates visible.</t>
+  </si>
+  <si>
+    <t>Opened GPay, minimized app, waited 5 minutes, re-opened GPay. App displayed lock screen requiring fingerprint or PIN authentication before showing home screen</t>
+  </si>
+  <si>
+    <t>Locked the app, re-opened GPay. Fingerprint prompt appeared automatically. Used registered fingerprint — app unlocked and home screen displayed immediately</t>
+  </si>
+  <si>
+    <t>Locked the app, re-opened GPay. Used an unregistered finger on the fingerprint sensor. Authentication failed. App showed "Fingerprint not recognised. Try again or use PIN." PIN fallback option displayed</t>
+  </si>
+  <si>
+    <t>Started a ₹1 payment, entered UPI PIN, then turned off internet before confirmation. App showed "Transaction timed out. Please check your transaction history before retrying." Balance remained unchanged. No duplicate deduction occurred.</t>
+  </si>
+  <si>
+    <t>Rotated phone to landscape while using GPay. App automatically locked back to portrait mode. No broken UI, overlapping elements, or crashes observed</t>
+  </si>
+  <si>
+    <t>Set phone font size to largest in Android Settings. Opened GPay and navigated through home, send money, and transaction history screens. All text remained readable. Some button labels appeared slightly cramped but no text was cut off or overlapping.</t>
+  </si>
+  <si>
+    <t>Enabled 2G mode via Developer Options. Opened GPay — home screen loaded in approximately 8 seconds with a loading spinner visible. Navigation between screens was slow but app remained functional. No crash occurred</t>
+  </si>
+  <si>
+    <t>Used GPay for 30 minutes — navigated home, sent money, checked history, viewed offers, scanned QR. Checked RAM usage in Developer Options. GPay was using approximately 180–220 MB RAM. No excessive memory increase over time. App remained smooth throughout.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redmi Note 13 pro + 5g </t>
+  </si>
+  <si>
+    <t>Memory usage within acceptable range for a payment app. No memory leak observed during 30-minute session.</t>
+  </si>
+  <si>
+    <t>Loading time on 2G is noticeably slow (~8 seconds). Loading spinner shown to user which is correct behaviour. App did not crash or freeze.</t>
+  </si>
+  <si>
+    <t>Minor observation — a few button labels look tight at maximum font size but remain readable. Not a breaking issue.</t>
+  </si>
+  <si>
+    <t>GPay is portrait-only by design. Landscape lock is intentional and handled correctly.</t>
+  </si>
+  <si>
+    <t>This is a critical test. App handled network failure gracefully. Always advised to check history before retrying — good user guidance.</t>
+  </si>
+  <si>
+    <t>Wrong fingerprint correctly rejected. Fallback PIN option provided as expected — good security behaviour.</t>
+  </si>
+  <si>
+    <t>Fingerprint authentication fast and responsive. No delay observed.</t>
+  </si>
+  <si>
+    <t>Security timeout working correctly. App does not expose home screen without re-authentication.</t>
+  </si>
+  <si>
+    <t>Offers section loaded quickly. Expiry dates and terms clearly visible for each offer.</t>
+  </si>
+  <si>
+    <t>Notification received instantly. Tapping notification deep-linked correctly to transaction detail.</t>
+  </si>
+  <si>
+    <t>Security feature working correctly. Brute force PIN attempt is blocked as expected.</t>
+  </si>
+  <si>
+    <t>PIN change process completed securely. Old PIN verified before allowing change.</t>
+  </si>
+  <si>
+    <t>Removal confirmation dialog prevents accidental deletion — good UX.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank linking process smooth and completed within 2 minutes.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date filter works accurately.
+</t>
+  </si>
+  <si>
+    <t>Transaction history loads quickly. All details displayed correctly.</t>
+  </si>
+  <si>
+    <t>App handles unreadable QR gracefully without crashing.</t>
+  </si>
+  <si>
+    <t>QR scan was fast and accurate. Merchant details loaded correctly.</t>
+  </si>
+  <si>
+    <t>Recharge for third-party number works as expected.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operator auto-detection worked correctly.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error handling for invalid account number works correctly.
+</t>
+  </si>
+  <si>
+    <t>Bill fetch and payment completed without any issues.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Request flow works correctly end to end.</t>
+  </si>
+  <si>
+    <t>App correctly validates UPI ID before allowing payment.</t>
+  </si>
+  <si>
+    <t>UPI daily limit enforced correctly by the app.</t>
+  </si>
+  <si>
+    <t>Pay button disabled automatically when ₹0 entered. No way to bypass this restriction. Input validation working at UI level.</t>
+  </si>
+  <si>
+    <t>App correctly blocked transaction after PIN entry. No duplicate charge or partial deduction observed. Critical financial safety feature working.</t>
+  </si>
+  <si>
+    <t>GPay contact detection worked instantly. Payment flow completed without any friction. SMS notification received promptly.</t>
+  </si>
+  <si>
+    <t>UPI daily limit enforced correctly. Transaction blocked before deduction. No amount was debited from account.</t>
+  </si>
+  <si>
+    <t>Waited full 10 minutes to confirm timeout behaviour. Resend OTP button functional after expiry. Expected security behaviour confirmed.</t>
+  </si>
+  <si>
+    <t>Error message shown in red — visually clear to user. Resend OTP option easily accessible. Security working correctly.</t>
+  </si>
+  <si>
+    <t>Error message was clear and user-friendly. Registration prompt shown immediately. Good UX for new users.</t>
+  </si>
+  <si>
+    <t>OTP received within 10 seconds. Login flow smooth and fast. No unnecessary steps in the process.</t>
+  </si>
+  <si>
+    <t>Banner message appeared at top of screen clearly. App remained stable without internet. Good offline error handling.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tested on Redmi Note 13 Pro+ 5G. App launch time excellent at ~2 seconds. No performance issues observed.
+</t>
+  </si>
+  <si>
+    <t>Button labels appear cramped at maximum font size</t>
+  </si>
+  <si>
+    <t>Step 1: Set phone font to largest in Android Settings
+Step 2: Open GPay
+Step 3:Navigate to Send Money screen.</t>
+  </si>
+  <si>
+    <t>All button labels fully visible and readable</t>
+  </si>
+  <si>
+    <t>Some button labels appear slightly squeezed and text is partially cut at edges</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Android 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Android 16</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Android 17</t>
+  </si>
+  <si>
+    <t>Redmi Note 13 Pro+ 5G</t>
+  </si>
+  <si>
+    <t>Reproducible consistently at maximum font size setting</t>
+  </si>
+  <si>
+    <t>App home screen takes ~8 seconds to load on 2G network</t>
+  </si>
+  <si>
+    <t>Step 1: Enable 2G mode in Developer Options
+Step 2: Launch GPay
+Step 3: Observe load time</t>
+  </si>
+  <si>
+    <t>App should load within 3-4 seconds even on slow network</t>
+  </si>
+  <si>
+    <t>App took approximately 8 seconds to fully load home screen on 2G</t>
+  </si>
+  <si>
+    <t>Loading spinner shown during wait which is correct, but load time is high on 2G</t>
+  </si>
+  <si>
+    <t>App forces portrait mode — no landscape support</t>
+  </si>
+  <si>
+    <t>Step 1: Enable auto-rotate on phone
+Step 2: Open GPay
+Step 3: Rotate phone to landscape.</t>
+  </si>
+  <si>
+    <t>App should either support landscape or display a proper message explaining portrait-only mode</t>
+  </si>
+  <si>
+    <t>App silently locks to portrait with no message or explanation to the user</t>
+  </si>
+  <si>
+    <t>Trivial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low </t>
+  </si>
+  <si>
+    <t>Not a breaking issue but a UX improvement opportunity. User is given no feedback about portrait-only restriction.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -932,6 +1200,23 @@
       <sz val="9"/>
       <color rgb="FF888888"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF888888"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1004,7 +1289,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1056,6 +1341,27 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1488,1246 +1794,1316 @@
       <c r="F5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="H5" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5" s="2"/>
+      <c r="K5" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L5" s="19" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="6" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="G6" s="20" t="s">
+        <v>247</v>
+      </c>
+      <c r="H6" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L6" s="3"/>
+      <c r="K6" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L6" s="20" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="7" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L7" s="2"/>
+      <c r="K7" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L7" s="19" t="s">
+        <v>314</v>
+      </c>
     </row>
     <row r="8" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="H8" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L8" s="3"/>
+        <v>32</v>
+      </c>
+      <c r="K8" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L8" s="20" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="9" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="H9" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="J9" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L9" s="2"/>
+        <v>32</v>
+      </c>
+      <c r="K9" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L9" s="19" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="10" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="G10" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="H10" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L10" s="3"/>
+      <c r="K10" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L10" s="20" t="s">
+        <v>311</v>
+      </c>
     </row>
     <row r="11" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="H11" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="J11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="I11" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L11" s="2"/>
+      <c r="K11" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L11" s="19" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="12" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="F12" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="20" t="s">
+        <v>253</v>
+      </c>
+      <c r="H12" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L12" s="3"/>
+      <c r="K12" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L12" s="20" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="13" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="H13" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="J13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L13" s="2"/>
+        <v>32</v>
+      </c>
+      <c r="K13" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L13" s="19" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="14" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>26</v>
+      <c r="G14" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="H14" s="20" t="s">
+        <v>246</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L14" s="3"/>
+        <v>32</v>
+      </c>
+      <c r="K14" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L14" s="20" t="s">
+        <v>307</v>
+      </c>
     </row>
     <row r="15" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="H15" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="J15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L15" s="2"/>
+        <v>32</v>
+      </c>
+      <c r="K15" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L15" s="19" t="s">
+        <v>306</v>
+      </c>
     </row>
     <row r="16" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="20" t="s">
+        <v>257</v>
+      </c>
+      <c r="H16" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="I16" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L16" s="3"/>
+      <c r="K16" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L16" s="20" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="17" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>26</v>
+      <c r="G17" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="H17" s="20" t="s">
+        <v>246</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L17" s="2"/>
+        <v>32</v>
+      </c>
+      <c r="K17" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L17" s="19" t="s">
+        <v>304</v>
+      </c>
     </row>
     <row r="18" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="H18" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="J18" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L18" s="3"/>
+        <v>32</v>
+      </c>
+      <c r="K18" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L18" s="20" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="19" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="H19" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H19" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="J19" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L19" s="2"/>
+        <v>32</v>
+      </c>
+      <c r="K19" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L19" s="19" t="s">
+        <v>302</v>
+      </c>
     </row>
     <row r="20" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="F20" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="G20" s="20" t="s">
+        <v>261</v>
+      </c>
+      <c r="H20" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="J20" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L20" s="3"/>
+        <v>32</v>
+      </c>
+      <c r="K20" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L20" s="20" t="s">
+        <v>301</v>
+      </c>
     </row>
     <row r="21" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>26</v>
+      <c r="G21" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="H21" s="20" t="s">
+        <v>246</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L21" s="2"/>
+        <v>32</v>
+      </c>
+      <c r="K21" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L21" s="19" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="22" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="F22" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G22" s="3" t="s">
+      <c r="G22" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="H22" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L22" s="3"/>
+      <c r="K22" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L22" s="20" t="s">
+        <v>299</v>
+      </c>
     </row>
     <row r="23" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="F23" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="G23" s="2" t="s">
+      <c r="G23" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="H23" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H23" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="J23" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L23" s="2"/>
+        <v>32</v>
+      </c>
+      <c r="K23" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L23" s="19" t="s">
+        <v>298</v>
+      </c>
     </row>
     <row r="24" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>26</v>
+      <c r="G24" s="20" t="s">
+        <v>265</v>
+      </c>
+      <c r="H24" s="20" t="s">
+        <v>246</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L24" s="3"/>
+        <v>54</v>
+      </c>
+      <c r="K24" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L24" s="20" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="25" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C25" s="2" t="s">
+      <c r="F25" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="G25" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="H25" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="J25" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L25" s="2"/>
+        <v>54</v>
+      </c>
+      <c r="K25" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L25" s="19" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="26" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="E26" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="F26" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="G26" s="3" t="s">
+      <c r="G26" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="H26" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L26" s="3"/>
+      <c r="K26" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L26" s="20" t="s">
+        <v>295</v>
+      </c>
     </row>
     <row r="27" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="F27" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>26</v>
+      <c r="G27" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="H27" s="20" t="s">
+        <v>246</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L27" s="2"/>
+        <v>32</v>
+      </c>
+      <c r="K27" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L27" s="19" t="s">
+        <v>294</v>
+      </c>
     </row>
     <row r="28" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="E28" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="F28" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="G28" s="3" t="s">
+      <c r="G28" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="H28" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H28" s="3" t="s">
+      <c r="J28" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="I28" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L28" s="3"/>
+      <c r="K28" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L28" s="20" t="s">
+        <v>293</v>
+      </c>
     </row>
     <row r="29" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="G29" s="2" t="s">
+      <c r="G29" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="H29" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H29" s="2" t="s">
+      <c r="J29" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="I29" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L29" s="2"/>
+      <c r="K29" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L29" s="19" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="30" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="E30" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="F30" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>26</v>
+      <c r="G30" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="H30" s="20" t="s">
+        <v>246</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L30" s="3"/>
+        <v>54</v>
+      </c>
+      <c r="K30" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L30" s="20" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="31" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="F31" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>26</v>
+      <c r="G31" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="H31" s="20" t="s">
+        <v>246</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L31" s="2"/>
+        <v>54</v>
+      </c>
+      <c r="K31" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L31" s="19" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="32" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="E32" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="F32" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="G32" s="3" t="s">
+      <c r="G32" s="20" t="s">
+        <v>273</v>
+      </c>
+      <c r="H32" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="J32" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L32" s="3"/>
+        <v>32</v>
+      </c>
+      <c r="K32" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L32" s="20" t="s">
+        <v>289</v>
+      </c>
     </row>
     <row r="33" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C33" s="2" t="s">
+      <c r="F33" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="G33" s="2" t="s">
+      <c r="G33" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="H33" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="I33" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H33" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="J33" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L33" s="2"/>
+        <v>32</v>
+      </c>
+      <c r="K33" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L33" s="19" t="s">
+        <v>288</v>
+      </c>
     </row>
     <row r="34" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E34" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="C34" s="3" t="s">
+      <c r="F34" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="G34" s="3" t="s">
+      <c r="G34" s="20" t="s">
+        <v>275</v>
+      </c>
+      <c r="H34" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H34" s="3" t="s">
+      <c r="J34" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="I34" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L34" s="3"/>
+      <c r="K34" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L34" s="20" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="35" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="E35" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="F35" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G35" s="2" t="s">
+      <c r="G35" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="H35" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="I35" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H35" s="2" t="s">
+      <c r="J35" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="I35" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L35" s="2"/>
+      <c r="K35" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L35" s="19" t="s">
+        <v>286</v>
+      </c>
     </row>
     <row r="36" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="E36" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="F36" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>26</v>
+      <c r="G36" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="H36" s="20" t="s">
+        <v>246</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L36" s="3"/>
+        <v>54</v>
+      </c>
+      <c r="K36" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L36" s="20" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="37" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C37" s="2" t="s">
+      <c r="F37" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>26</v>
+      <c r="G37" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="H37" s="20" t="s">
+        <v>246</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K37" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L37" s="2"/>
+        <v>54</v>
+      </c>
+      <c r="K37" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L37" s="19" t="s">
+        <v>284</v>
+      </c>
     </row>
     <row r="38" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="E38" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="F38" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>26</v>
+      <c r="G38" s="20" t="s">
+        <v>279</v>
+      </c>
+      <c r="H38" s="20" t="s">
+        <v>246</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L38" s="3"/>
+        <v>32</v>
+      </c>
+      <c r="K38" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L38" s="20" t="s">
+        <v>283</v>
+      </c>
     </row>
     <row r="39" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C39" s="2" t="s">
+      <c r="F39" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="D39" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>26</v>
+      <c r="G39" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="H39" s="20" t="s">
+        <v>246</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L39" s="2"/>
+        <v>54</v>
+      </c>
+      <c r="K39" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L39" s="19" t="s">
+        <v>282</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -2760,13 +3136,13 @@
     <col min="11" max="11" width="22" customWidth="1"/>
     <col min="12" max="13" width="14" customWidth="1"/>
     <col min="14" max="14" width="20" customWidth="1"/>
-    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="15" max="15" width="18.5" customWidth="1"/>
     <col min="16" max="16" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B1" s="14"/>
       <c r="C1" s="14"/>
@@ -2786,19 +3162,19 @@
     </row>
     <row r="2" spans="1:16" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>12</v>
@@ -2816,268 +3192,255 @@
         <v>14</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>220</v>
+        <v>17</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>17</v>
+        <v>217</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="P2" s="4" t="s">
         <v>18</v>
       </c>
+      <c r="P2" s="22"/>
     </row>
     <row r="3" spans="1:16" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="E3" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="B3" s="21">
+        <v>46115</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>189</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>317</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>318</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>319</v>
+      </c>
+      <c r="G3" s="22" t="s">
+        <v>320</v>
+      </c>
+      <c r="H3" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="I3" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>321</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>322</v>
+      </c>
+      <c r="L3" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="M3" s="22" t="s">
+        <v>325</v>
+      </c>
+      <c r="N3" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>236</v>
+      <c r="O3" s="22" t="s">
+        <v>326</v>
       </c>
       <c r="P3" s="5"/>
     </row>
     <row r="4" spans="1:16" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="E4" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="B4" s="21">
+        <v>46115</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>327</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>328</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>329</v>
+      </c>
+      <c r="G4" s="23" t="s">
+        <v>330</v>
+      </c>
+      <c r="H4" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="I4" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="J4" s="23" t="s">
+        <v>321</v>
+      </c>
+      <c r="K4" s="23" t="s">
+        <v>322</v>
+      </c>
+      <c r="L4" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="M4" s="22" t="s">
+        <v>325</v>
+      </c>
+      <c r="N4" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="G4" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="O4" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="P4" s="6"/>
+      <c r="O4" s="23" t="s">
+        <v>331</v>
+      </c>
     </row>
     <row r="5" spans="1:16" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="E5" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="B5" s="21">
+        <v>46115</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>189</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>332</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>333</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>334</v>
+      </c>
+      <c r="G5" s="22" t="s">
+        <v>335</v>
+      </c>
+      <c r="H5" s="22" t="s">
+        <v>336</v>
+      </c>
+      <c r="I5" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="J5" s="22" t="s">
+        <v>321</v>
+      </c>
+      <c r="K5" s="23" t="s">
+        <v>322</v>
+      </c>
+      <c r="L5" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="M5" s="22" t="s">
+        <v>325</v>
+      </c>
+      <c r="N5" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="P5" s="5"/>
+      <c r="O5" s="22" t="s">
+        <v>338</v>
+      </c>
     </row>
     <row r="6" spans="1:16" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="B6" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="C6" s="22"/>
+      <c r="D6" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H6" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="I6" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="J6" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="K6" s="23" t="s">
+        <v>323</v>
+      </c>
+      <c r="L6" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="M6" s="22" t="s">
+        <v>325</v>
+      </c>
+      <c r="N6" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="G6" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="O6" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="P6" s="6"/>
+      <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:16" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="B7" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="C7" s="22"/>
+      <c r="D7" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="I7" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="J7" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="K7" s="23" t="s">
+        <v>324</v>
+      </c>
+      <c r="L7" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="M7" s="22" t="s">
+        <v>325</v>
+      </c>
+      <c r="N7" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="M7" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="O7" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="P7" s="5"/>
+      <c r="O7" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3093,7 +3456,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="B1" s="14"/>
       <c r="C1" s="14"/>
@@ -3107,7 +3470,7 @@
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="18" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="B3" s="8">
         <v>35</v>
@@ -3115,16 +3478,15 @@
     </row>
     <row r="4" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="B4" s="10">
-        <f>COUNTIF('Test Cases'!H5:H39,"Pass")</f>
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="B5" s="10">
         <f>COUNTIF('Test Cases'!H5:H39,"Fail")</f>
@@ -3133,7 +3495,7 @@
     </row>
     <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="B6" s="10">
         <f>COUNTIF('Test Cases'!H5:H39,"Blocked")</f>
@@ -3142,7 +3504,7 @@
     </row>
     <row r="7" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="B7" s="10">
         <f>COUNTIF('Test Cases'!H5:H39,"Skip")</f>
@@ -3151,11 +3513,11 @@
     </row>
     <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="B8" s="10">
         <f>COUNTIF('Test Cases'!H5:H39,"(Pass / Fail / Blocked / Skip)")</f>
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -3164,16 +3526,15 @@
     </row>
     <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="B10" s="11">
-        <f>COUNTA('Bug Report'!A3:A100)-COUNTBLANK('Bug Report'!A3:A100)</f>
-        <v>-88</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="B11" s="10">
         <f>COUNTIF('Bug Report'!H3:H100,"Critical")</f>
@@ -3182,7 +3543,7 @@
     </row>
     <row r="12" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="B12" s="10">
         <f>COUNTIF('Bug Report'!H3:H100,"Major")</f>
@@ -3191,20 +3552,20 @@
     </row>
     <row r="13" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="B13" s="10">
         <f>COUNTIF('Bug Report'!H3:H100,"Minor")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="B14" s="10">
         <f>COUNTIF('Bug Report'!H3:H100,"Trivial")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -3213,11 +3574,10 @@
     </row>
     <row r="16" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
-        <v>253</v>
-      </c>
-      <c r="B16" s="12">
-        <f>IFERROR(COUNTIF('Test Cases'!H5:H39,"Pass")/35*100,0)</f>
-        <v>0</v>
+        <v>244</v>
+      </c>
+      <c r="B16" s="25">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
